--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_14_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_14_9.xlsx
@@ -513,111 +513,111 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_14_9_0</t>
+          <t>model_14_9_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9987129569044852</v>
+        <v>0.9999608457922458</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6803158560232244</v>
+        <v>0.6985306582612965</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9991107439575613</v>
+        <v>0.9999990745931499</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9976482865539708</v>
+        <v>0.9999848510171193</v>
       </c>
       <c r="F2" t="n">
-        <v>0.99886954549945</v>
+        <v>0.99999508066945</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007640443788643511</v>
+        <v>2.324362909665453e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1897783175005774</v>
+        <v>0.1789652240535712</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006902236088055023</v>
+        <v>4.112168328119129e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003606242889355227</v>
+        <v>4.102787743212765e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005254239488705125</v>
+        <v>2.257002288012338e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01262792828653141</v>
+        <v>0.001884700404310031</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02764135269599429</v>
+        <v>0.00482116470333202</v>
       </c>
       <c r="N2" t="n">
-        <v>1.001144038307124</v>
+        <v>1.000034803740226</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02881810230575097</v>
+        <v>0.005026411665939635</v>
       </c>
       <c r="P2" t="n">
-        <v>116.353769365932</v>
+        <v>123.3389589616574</v>
       </c>
       <c r="Q2" t="n">
-        <v>178.5164364342102</v>
+        <v>185.5016260299357</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_14_9_1</t>
+          <t>model_14_9_0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9988055510842049</v>
+        <v>0.999960831951723</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6795004345637099</v>
+        <v>0.6985302369723916</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9990396904270906</v>
+        <v>0.9999990718399963</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9978834445435901</v>
+        <v>0.9999848599352106</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9988490161649616</v>
+        <v>0.9999950819683521</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007090764739225009</v>
+        <v>2.325184542879878e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1902623869033182</v>
+        <v>0.1789654741488639</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007453740063055763</v>
+        <v>4.124402331725662e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003245639079664161</v>
+        <v>4.100372463181657e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005349657782757282</v>
+        <v>2.256406348177111e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01217762455891893</v>
+        <v>0.001884543672855107</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02662848989189024</v>
+        <v>0.004822016738751409</v>
       </c>
       <c r="N3" t="n">
-        <v>1.001061732369596</v>
+        <v>1.000034816042913</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02776211983516116</v>
+        <v>0.005027299974270784</v>
       </c>
       <c r="P3" t="n">
-        <v>116.5030943511619</v>
+        <v>123.3382521115983</v>
       </c>
       <c r="Q3" t="n">
-        <v>178.6657614194401</v>
+        <v>185.5009191798765</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +627,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9988849118465927</v>
+        <v>0.9999640406371686</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6787164004315092</v>
+        <v>0.6982775495899187</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9989656116440097</v>
+        <v>0.9999967842500821</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9980437562949067</v>
+        <v>0.9999822464583455</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9988135931543541</v>
+        <v>0.9999932033544716</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006619644971626949</v>
+        <v>2.134703114030178e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1907278234327036</v>
+        <v>0.1791154802946263</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000802872547281269</v>
+        <v>1.4289612143116e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0002999808485702328</v>
+        <v>4.808178454758057e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005514300394248256</v>
+        <v>3.118319525852925e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0117728423168538</v>
+        <v>0.001872399823839254</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02572867072280834</v>
+        <v>0.004620284746668952</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000991189469695</v>
+        <v>1.000031963878072</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02682399350116898</v>
+        <v>0.004816979833642583</v>
       </c>
       <c r="P4" t="n">
-        <v>116.640597266258</v>
+        <v>123.5091957692385</v>
       </c>
       <c r="Q4" t="n">
-        <v>178.8032643345362</v>
+        <v>185.6718628375168</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9989525126571791</v>
+        <v>0.9999662235600408</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6779630910161251</v>
+        <v>0.6980192913069492</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9988891603196309</v>
+        <v>0.999990868921269</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9981392262643571</v>
+        <v>0.9999760497703178</v>
       </c>
       <c r="F5" t="n">
-        <v>0.998765513909245</v>
+        <v>0.9999885090270968</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0006218337357956187</v>
+        <v>2.0051153825968e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1911750204429479</v>
+        <v>0.1792687935675739</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0008622126096393984</v>
+        <v>4.057516188912284e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002853409740115771</v>
+        <v>6.486422854974674e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0005737767918254877</v>
+        <v>5.272089742713966e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01143668660778309</v>
+        <v>0.001862257676379052</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0249365943102826</v>
+        <v>0.004477851474308633</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000931099860285</v>
+        <v>1.000030023502186</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02599819675593781</v>
+        <v>0.004668482882000365</v>
       </c>
       <c r="P5" t="n">
-        <v>116.765675613505</v>
+        <v>123.6344477168753</v>
       </c>
       <c r="Q5" t="n">
-        <v>178.9283426817832</v>
+        <v>185.7971147851536</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +737,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9990097206286269</v>
+        <v>0.9999675171799247</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6772397693685398</v>
+        <v>0.6977639906932899</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9988111186233048</v>
+        <v>0.9999821509197495</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9981792271570208</v>
+        <v>0.9999667641143132</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9987069566174112</v>
+        <v>0.9999815468336848</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0005878726126885303</v>
+        <v>1.92832051814285e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1916044154188228</v>
+        <v>0.1794203510402544</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009227870884224782</v>
+        <v>7.93147602899347e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002792070236793274</v>
+        <v>9.001250150190327e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0006009936355776831</v>
+        <v>8.466363089591898e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01126562131074081</v>
+        <v>0.001851568417387927</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0242460844815927</v>
+        <v>0.004391264644886311</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000880248330109</v>
+        <v>1.000028873617845</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02527829049428817</v>
+        <v>0.004578209871990088</v>
       </c>
       <c r="P6" t="n">
-        <v>116.8780005572482</v>
+        <v>123.7125520774976</v>
       </c>
       <c r="Q6" t="n">
-        <v>179.0406676255265</v>
+        <v>185.8752191457759</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +792,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9990577368821829</v>
+        <v>0.9999680790766776</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6765454704333225</v>
+        <v>0.6975121768394306</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9987320027448566</v>
+        <v>0.999971328336359</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9981714570325279</v>
+        <v>0.9999549365040232</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9986396065474248</v>
+        <v>0.999972814952732</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0005593680903835078</v>
+        <v>1.8949638996257e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1920165812589201</v>
+        <v>0.1795698386216973</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009841953269165277</v>
+        <v>1.274063479399946e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002803985360317173</v>
+        <v>1.220451303002875e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0006322972746996094</v>
+        <v>1.24725739120141e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01110339253034547</v>
+        <v>0.001840169704363059</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02365096383624794</v>
+        <v>0.00435311830717441</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000837567215837</v>
+        <v>1.000028374154064</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02465783433100152</v>
+        <v>0.004538439565707986</v>
       </c>
       <c r="P7" t="n">
-        <v>116.9774056427969</v>
+        <v>123.7474513538935</v>
       </c>
       <c r="Q7" t="n">
-        <v>179.1400727110752</v>
+        <v>185.9101184221717</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +847,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9990976258530019</v>
+        <v>0.9999680431195931</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6758793151047306</v>
+        <v>0.6972640872298062</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9986522976706097</v>
+        <v>0.9999589994656768</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9981228590301695</v>
+        <v>0.9999410258224796</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9985650342963021</v>
+        <v>0.9999627388171243</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0005356882741915232</v>
+        <v>1.89709846748884e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.192412039838384</v>
+        <v>0.1797171153308836</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001046060887971323</v>
+        <v>1.821913233605523e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002878508130400985</v>
+        <v>1.597193254503523e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0006669577114018131</v>
+        <v>1.709553244054523e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01094952457014842</v>
+        <v>0.001828067178791212</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02314494057437874</v>
+        <v>0.004355569385842499</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000802110352887</v>
+        <v>1.000028406115917</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02413026861126199</v>
+        <v>0.004540994991869408</v>
       </c>
       <c r="P8" t="n">
-        <v>117.0639162881529</v>
+        <v>123.745199736824</v>
       </c>
       <c r="Q8" t="n">
-        <v>179.2265833564311</v>
+        <v>185.9078668051022</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +902,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9991303783704976</v>
+        <v>0.9999675174686682</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6752405456068628</v>
+        <v>0.6970203056445317</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9985725244978894</v>
+        <v>0.9999456190682435</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9980397945196129</v>
+        <v>0.9999254092413616</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9984847104097462</v>
+        <v>0.999951648952153</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0005162449649710343</v>
+        <v>1.928303377084281e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.192791241005724</v>
+        <v>0.1798618346107186</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00110797930576461</v>
+        <v>2.416488976506183e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003005883683344521</v>
+        <v>2.020135957033201e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0007042914507449773</v>
+        <v>2.218359276887778e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01080339506283587</v>
+        <v>0.001815512708406993</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02272102473417593</v>
+        <v>0.004391245127619592</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000772997004002</v>
+        <v>1.000028873361184</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02368830579611498</v>
+        <v>0.004578189523832919</v>
       </c>
       <c r="P9" t="n">
-        <v>117.1378583336387</v>
+        <v>123.7125698558022</v>
       </c>
       <c r="Q9" t="n">
-        <v>179.3005254019169</v>
+        <v>185.8752369240805</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +957,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9991568094434664</v>
+        <v>0.9999666030162291</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6746284139902272</v>
+        <v>0.696781055592502</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9984929640460898</v>
+        <v>0.9999316102765348</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9979276406503736</v>
+        <v>0.9999084522656447</v>
       </c>
       <c r="F10" t="n">
-        <v>0.998399794656604</v>
+        <v>0.9999398612044416</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005005543382938175</v>
+        <v>1.982589224102013e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1931546287760678</v>
+        <v>0.1800038637766675</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001169732613629352</v>
+        <v>3.038988254198745e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0003177866411146853</v>
+        <v>2.479380466587082e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0007437594437650958</v>
+        <v>2.759184360392913e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01066481998285226</v>
+        <v>0.001802392392436803</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02237307172235894</v>
+        <v>0.004452627565945767</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000749502716919</v>
+        <v>1.000029686207796</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02332553970422292</v>
+        <v>0.004642185139637803</v>
       </c>
       <c r="P10" t="n">
-        <v>117.1995887941649</v>
+        <v>123.6570435712078</v>
       </c>
       <c r="Q10" t="n">
-        <v>179.3622558624432</v>
+        <v>185.819710639486</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1012,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9991777383248523</v>
+        <v>0.999965388118314</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6740417955643367</v>
+        <v>0.6965468224264602</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9984140235947494</v>
+        <v>0.9999173385609406</v>
       </c>
       <c r="E11" t="n">
-        <v>0.997791300611248</v>
+        <v>0.9998904820709762</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9983113896227018</v>
+        <v>0.9999276460625226</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0004881300502224981</v>
+        <v>2.054710812423441e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1935028708142729</v>
+        <v>0.180142914702376</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001231004688942381</v>
+        <v>3.673170904171499e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0003386937502466103</v>
+        <v>2.96606590949632e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007848492195944955</v>
+        <v>3.31961840683391e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0105332294196048</v>
+        <v>0.001788817463415046</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02209366538676863</v>
+        <v>0.004532891805926368</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000730899266798</v>
+        <v>1.000030766117054</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02303423846247567</v>
+        <v>0.00472586639448426</v>
       </c>
       <c r="P11" t="n">
-        <v>117.2498573825148</v>
+        <v>123.5855807016122</v>
       </c>
       <c r="Q11" t="n">
-        <v>179.412524450793</v>
+        <v>185.7482477698904</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1067,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9991938419043045</v>
+        <v>0.9999639346144266</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6734799803078571</v>
+        <v>0.6963177273470795</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9983360041991362</v>
+        <v>0.9999030301372975</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9976349192632784</v>
+        <v>0.9998717291619246</v>
       </c>
       <c r="F12" t="n">
-        <v>0.998220447993668</v>
+        <v>0.9999151825695737</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000478570269821314</v>
+        <v>2.140997081995813e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1938363886196746</v>
+        <v>0.1802789154378884</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001291561858336797</v>
+        <v>4.308984725078697e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0003626741006203103</v>
+        <v>3.473949547706313e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0008271179794785536</v>
+        <v>3.891446866335379e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01040824887083976</v>
+        <v>0.001774928543077998</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02187624898883065</v>
+        <v>0.004627090967331216</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000716584973952</v>
+        <v>1.00003205812051</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02280756619836348</v>
+        <v>0.004824075809209259</v>
       </c>
       <c r="P12" t="n">
-        <v>117.2894150069446</v>
+        <v>123.5033076365602</v>
       </c>
       <c r="Q12" t="n">
-        <v>179.4520820752228</v>
+        <v>185.6659747048384</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1122,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9992057072399577</v>
+        <v>0.9999623044260986</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6729421378679432</v>
+        <v>0.6960941329461973</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9982590870298711</v>
+        <v>0.9998889104700889</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9974621542805583</v>
+        <v>0.999852431052757</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9981277233128363</v>
+        <v>0.9999026484537814</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004715264940217644</v>
+        <v>2.237772103186973e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1941556751255911</v>
+        <v>0.1804116507330273</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001351263500626119</v>
+        <v>4.936410902959953e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0003891668049723608</v>
+        <v>3.996598800022281e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0008702154840103219</v>
+        <v>4.466515521175573e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01028972495933041</v>
+        <v>0.001760829742077801</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02171466080835168</v>
+        <v>0.004730509595368107</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000706038008927</v>
+        <v>1.000033507176801</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02263909887450788</v>
+        <v>0.004931897182347754</v>
       </c>
       <c r="P13" t="n">
-        <v>117.3190705330862</v>
+        <v>123.4148893816688</v>
       </c>
       <c r="Q13" t="n">
-        <v>179.4817376013644</v>
+        <v>185.5775564499471</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1177,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9992138846275248</v>
+        <v>0.9999605521295449</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6724273775290156</v>
+        <v>0.6958760423877594</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9981834804743267</v>
+        <v>0.999875165750826</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9972762091871651</v>
+        <v>0.9998327931801186</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9980339201769619</v>
+        <v>0.9998901960800567</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0004666720435171644</v>
+        <v>2.341795996141294e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1944612590992674</v>
+        <v>0.1805411187095376</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001409947869499337</v>
+        <v>5.547175770554883e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0004176806178262161</v>
+        <v>4.528449841098912e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0009138142436627764</v>
+        <v>5.037833827638237e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01017719409589718</v>
+        <v>0.001746545696535764</v>
       </c>
       <c r="M14" t="n">
-        <v>0.021602593444241</v>
+        <v>0.004839210675452448</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000698769219978</v>
+        <v>1.000035064773738</v>
       </c>
       <c r="O14" t="n">
-        <v>0.02252226057069559</v>
+        <v>0.005045225892453541</v>
       </c>
       <c r="P14" t="n">
-        <v>117.3397676185458</v>
+        <v>123.3240146205495</v>
       </c>
       <c r="Q14" t="n">
-        <v>179.5024346868241</v>
+        <v>185.4866816888277</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1232,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9992188694552918</v>
+        <v>0.999958713065097</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6719350768827246</v>
+        <v>0.695663810927031</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9981093866256524</v>
+        <v>0.9998618738432815</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9970801566455245</v>
+        <v>0.9998129869266099</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9979397074992062</v>
+        <v>0.9998779139733202</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0004637128344213536</v>
+        <v>2.450970806115064e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1947535100291864</v>
+        <v>0.1806671084725477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001467458104101746</v>
+        <v>6.137819347642535e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.000447744360729299</v>
+        <v>5.064861128735332e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0009576033542868665</v>
+        <v>5.601340238188934e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01007036204964877</v>
+        <v>0.00173204842526276</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02153399253323344</v>
+        <v>0.004950728033446257</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000694338261963</v>
+        <v>1.000036699497691</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02245073917688297</v>
+        <v>0.005161490775249901</v>
       </c>
       <c r="P15" t="n">
-        <v>117.3524901773272</v>
+        <v>123.2328825430099</v>
       </c>
       <c r="Q15" t="n">
-        <v>179.5151572456055</v>
+        <v>185.3955496112881</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1287,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9992210854468835</v>
+        <v>0.9999568173007458</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6714641614164216</v>
+        <v>0.6954574521602591</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9980369241566928</v>
+        <v>0.9998491399859928</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9968760458557734</v>
+        <v>0.9997931028491802</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9978455264749275</v>
+        <v>0.9998658779627482</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000462397326086659</v>
+        <v>2.563511567275096e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1950330657924728</v>
+        <v>0.1807896119507381</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001523702092830868</v>
+        <v>6.703665219949523e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0004790437983977468</v>
+        <v>5.603380115825117e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001001377752691295</v>
+        <v>6.153555689519116e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00996897863567265</v>
+        <v>0.001717597915320887</v>
       </c>
       <c r="M16" t="n">
-        <v>0.02150342591511081</v>
+        <v>0.005063113239179128</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000692368491659</v>
+        <v>1.000038384621559</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02241887127454523</v>
+        <v>0.005278660451860269</v>
       </c>
       <c r="P16" t="n">
-        <v>117.3581720466148</v>
+        <v>123.1430948808822</v>
       </c>
       <c r="Q16" t="n">
-        <v>179.520839114893</v>
+        <v>185.3057619491605</v>
       </c>
     </row>
     <row r="17">
@@ -1342,52 +1342,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9992209244606324</v>
+        <v>0.9999548942498568</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6710138427964016</v>
+        <v>0.6952569261148507</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9979662103923466</v>
+        <v>0.9998370081662515</v>
       </c>
       <c r="E17" t="n">
-        <v>0.996666363868623</v>
+        <v>0.999773292234483</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9977519123377815</v>
+        <v>0.9998541566191221</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004624928944795385</v>
+        <v>2.677672175196157e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1953003943780681</v>
+        <v>0.1809086528735666</v>
       </c>
       <c r="I17" t="n">
-        <v>0.001578588770334226</v>
+        <v>7.24275875370858e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0005111975532042257</v>
+        <v>6.139909517205319e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001044888667624609</v>
+        <v>6.691334135456949e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.009872730607481589</v>
+        <v>0.001703047563945772</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02150564796697692</v>
+        <v>0.005174622860843249</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000692511590549</v>
+        <v>1.000040094000127</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02242118792375957</v>
+        <v>0.00539491726897537</v>
       </c>
       <c r="P17" t="n">
-        <v>117.3577587288346</v>
+        <v>123.0559552784724</v>
       </c>
       <c r="Q17" t="n">
-        <v>179.5204257971128</v>
+        <v>185.2186223467507</v>
       </c>
     </row>
     <row r="18">
@@ -1397,52 +1397,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9992187067462802</v>
+        <v>0.9999529740355312</v>
       </c>
       <c r="C18" t="n">
-        <v>0.670583672579933</v>
+        <v>0.6950625025581811</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9978972863158646</v>
+        <v>0.999825578359559</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9964529272964487</v>
+        <v>0.9997536640107841</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9976591435101378</v>
+        <v>0.9998428288084732</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0004638094255192606</v>
+        <v>2.791664392457504e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1955557620009497</v>
+        <v>0.181024071095466</v>
       </c>
       <c r="I18" t="n">
-        <v>0.001632086326192885</v>
+        <v>7.750657404652018e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0005439270561133107</v>
+        <v>6.671499236771464e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001088006691153098</v>
+        <v>7.211057180950308e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.009781441699380354</v>
+        <v>0.001688588556666986</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0215362351751475</v>
+        <v>0.005283620342584717</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000694482892195</v>
+        <v>1.000041800857306</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02245307729270622</v>
+        <v>0.005508554999170464</v>
       </c>
       <c r="P18" t="n">
-        <v>117.3520736219412</v>
+        <v>122.9725749811393</v>
       </c>
       <c r="Q18" t="n">
-        <v>179.5147406902194</v>
+        <v>185.1352420494175</v>
       </c>
     </row>
     <row r="19">
@@ -1452,52 +1452,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.999214765934231</v>
+        <v>0.9999510713885041</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6701725812646995</v>
+        <v>0.6948741045065645</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9978303250569648</v>
+        <v>0.9998148490449096</v>
       </c>
       <c r="E19" t="n">
-        <v>0.996237175743875</v>
+        <v>0.9997343199855286</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9975676413819431</v>
+        <v>0.9998319239308306</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004661488617859519</v>
+        <v>2.904613738990123e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1957998035638925</v>
+        <v>0.1811359123172777</v>
       </c>
       <c r="I19" t="n">
-        <v>0.001684060380416042</v>
+        <v>8.227428760683167e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0005770115504699654</v>
+        <v>7.195392031073784e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001130535965443004</v>
+        <v>7.711375944634695e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.009694685046681277</v>
+        <v>0.001674122464545198</v>
       </c>
       <c r="M19" t="n">
-        <v>0.02159048081414474</v>
+        <v>0.005389446853796893</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000697985836239</v>
+        <v>1.000043492099107</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02250963228085952</v>
+        <v>0.005618886764056021</v>
       </c>
       <c r="P19" t="n">
-        <v>117.342011057916</v>
+        <v>122.8932500954199</v>
       </c>
       <c r="Q19" t="n">
-        <v>179.5046781261942</v>
+        <v>185.0559171636981</v>
       </c>
     </row>
     <row r="20">
@@ -1507,52 +1507,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9992093438795657</v>
+        <v>0.9999492020160559</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6697798963787189</v>
+        <v>0.6946917333550499</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9977653048284062</v>
+        <v>0.9998048323434433</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9960205699511099</v>
+        <v>0.9997153123641849</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9974776239268185</v>
+        <v>0.999821462393951</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0004693676276557773</v>
+        <v>3.015587762786458e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1960329182753143</v>
+        <v>0.1812441757108403</v>
       </c>
       <c r="I20" t="n">
-        <v>0.001734527843845295</v>
+        <v>8.672534202838282e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0006102270385759511</v>
+        <v>7.710174023309987e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001172375178534578</v>
+        <v>8.191354113074134e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.009612362539680376</v>
+        <v>0.001659822538186167</v>
       </c>
       <c r="M20" t="n">
-        <v>0.02166489389901961</v>
+        <v>0.005491436754426347</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000702805440386</v>
+        <v>1.000045153763506</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02258721328481384</v>
+        <v>0.005725218585903471</v>
       </c>
       <c r="P20" t="n">
-        <v>117.3282484845892</v>
+        <v>122.8182614151856</v>
       </c>
       <c r="Q20" t="n">
-        <v>179.4909155528674</v>
+        <v>184.9809284834638</v>
       </c>
     </row>
     <row r="21">
@@ -1562,52 +1562,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9992026873865937</v>
+        <v>0.9999473722966177</v>
       </c>
       <c r="C21" t="n">
-        <v>0.669404933795734</v>
+        <v>0.6945153301113154</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9977022791956554</v>
+        <v>0.9997954966118491</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9958044800854002</v>
+        <v>0.999696701522899</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9973893374506657</v>
+        <v>0.99981144848593</v>
       </c>
       <c r="G21" t="n">
-        <v>0.000473319209429514</v>
+        <v>3.1242078126149e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1962555122621144</v>
+        <v>0.1813488962965445</v>
       </c>
       <c r="I21" t="n">
-        <v>0.001783447139985582</v>
+        <v>9.087379843697769e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0006433634116741721</v>
+        <v>8.214210050809123e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.001213409849907436</v>
+        <v>8.650794947253447e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.009534196894780484</v>
+        <v>0.001645535307543491</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02175590056581235</v>
+        <v>0.005589461344901582</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000708722323028</v>
+        <v>1.000046780180784</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02268209429382172</v>
+        <v>0.005827416286134112</v>
       </c>
       <c r="P21" t="n">
-        <v>117.3114810714314</v>
+        <v>122.7474894277633</v>
       </c>
       <c r="Q21" t="n">
-        <v>179.4741481397096</v>
+        <v>184.9101564960415</v>
       </c>
     </row>
     <row r="22">
@@ -1617,52 +1617,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9991949976496147</v>
+        <v>0.9999455905555822</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6690470695494446</v>
+        <v>0.6943449762113685</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9976412745239214</v>
+        <v>0.999786826126581</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9955895859306628</v>
+        <v>0.9996785139500207</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9973029602344159</v>
+        <v>0.9998018824376562</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0004778841694795849</v>
+        <v>3.229979657204171e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1964679559376423</v>
+        <v>0.1814500257304583</v>
       </c>
       <c r="I22" t="n">
-        <v>0.001830797804663378</v>
+        <v>9.472664379924892e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0006763164280713897</v>
+        <v>8.706782731569514e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001253557116367384</v>
+        <v>9.089687853948208e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.009460034431862697</v>
+        <v>0.001631615481849019</v>
       </c>
       <c r="M22" t="n">
-        <v>0.02186056196623465</v>
+        <v>0.005683290998360168</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000715557644787</v>
+        <v>1.000048363950594</v>
       </c>
       <c r="O22" t="n">
-        <v>0.02279121134673896</v>
+        <v>0.005925240462194589</v>
       </c>
       <c r="P22" t="n">
-        <v>117.2922843562046</v>
+        <v>122.6808992516694</v>
       </c>
       <c r="Q22" t="n">
-        <v>179.4549514244829</v>
+        <v>184.8435663199476</v>
       </c>
     </row>
     <row r="23">
@@ -1672,52 +1672,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.999186469128907</v>
+        <v>0.9999438646348612</v>
       </c>
       <c r="C23" t="n">
-        <v>0.668705443417008</v>
+        <v>0.6941805682306164</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9975822836202455</v>
+        <v>0.9997788203574104</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9953770297443348</v>
+        <v>0.999660779602197</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9972186403094327</v>
+        <v>0.9997927704995438</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0004829470677846144</v>
+        <v>3.332437766789889e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1966707599673371</v>
+        <v>0.1815476254098877</v>
       </c>
       <c r="I23" t="n">
-        <v>0.001876585420916346</v>
+        <v>9.828411372933633e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0007089109279169417</v>
+        <v>9.187080751959428e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.001292748174416644</v>
+        <v>9.50774606244653e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.009389607924495844</v>
+        <v>0.001617807056709412</v>
       </c>
       <c r="M23" t="n">
-        <v>0.02197605669324263</v>
+        <v>0.005772727056417867</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000723138552083</v>
+        <v>1.000049898102346</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02291162292338272</v>
+        <v>0.006018483998401968</v>
       </c>
       <c r="P23" t="n">
-        <v>117.2712070016505</v>
+        <v>122.6184427334111</v>
       </c>
       <c r="Q23" t="n">
-        <v>179.4338740699287</v>
+        <v>184.7811098016894</v>
       </c>
     </row>
     <row r="24">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9991772533711061</v>
+        <v>0.9999422059161699</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6683794498274397</v>
+        <v>0.6940221202587159</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9975253087567183</v>
+        <v>0.9997714734036568</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9951674096386032</v>
+        <v>0.9996435869423952</v>
       </c>
       <c r="F24" t="n">
-        <v>0.997136488079794</v>
+        <v>0.9997841378427059</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0004884179397152491</v>
+        <v>3.430906473595343e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1968642838442947</v>
+        <v>0.1816416869706038</v>
       </c>
       <c r="I24" t="n">
-        <v>0.001920808225191154</v>
+        <v>0.0001015488302729925</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0007410551934964553</v>
+        <v>9.65270827601873e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.001330931709343805</v>
+        <v>9.903814715214553e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.009322694755229366</v>
+        <v>0.001604197347965187</v>
       </c>
       <c r="M24" t="n">
-        <v>0.02210017963083669</v>
+        <v>0.005857394022596861</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000731330336795</v>
+        <v>1.00005137251896</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02304103003140006</v>
+        <v>0.006106755412615982</v>
       </c>
       <c r="P24" t="n">
-        <v>117.2486781695972</v>
+        <v>122.5602019213831</v>
       </c>
       <c r="Q24" t="n">
-        <v>179.4113452378755</v>
+        <v>184.7228689896613</v>
       </c>
     </row>
     <row r="25">
@@ -1782,52 +1782,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9991675057527414</v>
+        <v>0.9999406045142425</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6680684555138175</v>
+        <v>0.6938694101779691</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9974703501739964</v>
+        <v>0.9997646952374182</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9949614455676851</v>
+        <v>0.9996268870038254</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9970566225114996</v>
+        <v>0.99977592608392</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0004942045470516612</v>
+        <v>3.525972609705872e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1970489035031157</v>
+        <v>0.1817323422712671</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001963466030694627</v>
+        <v>0.0001045607985250102</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0007726388231884626</v>
+        <v>0.0001010499146767534</v>
       </c>
       <c r="K25" t="n">
-        <v>0.001368052426941545</v>
+        <v>0.0001028057245043865</v>
       </c>
       <c r="L25" t="n">
-        <v>0.009259165682164981</v>
+        <v>0.001590906388394254</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02223071179813326</v>
+        <v>0.005937990072158989</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000739994886452</v>
+        <v>1.00005279598734</v>
       </c>
       <c r="O25" t="n">
-        <v>0.02317711922329727</v>
+        <v>0.006190782602864793</v>
       </c>
       <c r="P25" t="n">
-        <v>117.2251221272382</v>
+        <v>122.5055382982344</v>
       </c>
       <c r="Q25" t="n">
-        <v>179.3877891955165</v>
+        <v>184.6682053665127</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9991573327849839</v>
+        <v>0.9999390654007302</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6677717978513786</v>
+        <v>0.6937222878484128</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9974173411398497</v>
+        <v>0.9997584734412037</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9947594350562861</v>
+        <v>0.9996106970921094</v>
       </c>
       <c r="F26" t="n">
-        <v>0.996979047260147</v>
+        <v>0.9997681358700002</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000500243660161882</v>
+        <v>3.617341036417337e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1972250123064832</v>
+        <v>0.1818196804414454</v>
       </c>
       <c r="I26" t="n">
-        <v>0.002004610633713249</v>
+        <v>0.0001073255363624227</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0008036161929669911</v>
+        <v>0.0001054346164006606</v>
       </c>
       <c r="K26" t="n">
-        <v>0.001404108628124788</v>
+        <v>0.000106379895920958</v>
       </c>
       <c r="L26" t="n">
-        <v>0.009198850083867387</v>
+        <v>0.001577922804995079</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0223661275182335</v>
+        <v>0.006014433503179943</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000749037524459</v>
+        <v>1.00005416408824</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02331829987095137</v>
+        <v>0.006270480389004027</v>
       </c>
       <c r="P26" t="n">
-        <v>117.2008305158406</v>
+        <v>122.4543724587029</v>
       </c>
       <c r="Q26" t="n">
-        <v>179.3634975841188</v>
+        <v>184.6170395269812</v>
       </c>
     </row>
   </sheetData>
